--- a/bug-reports/Crouching_Camera_Bug/Roadside_Research_Camera_Bug.xlsx
+++ b/bug-reports/Crouching_Camera_Bug/Roadside_Research_Camera_Bug.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\qa-portfolio\bug-reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\qa-portfolio\bug-reports\Crouching_Camera_Bug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F299B1-2CEF-4BBB-A8B9-D57F867D60BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460F1DE1-BFAB-4A0B-98F0-DCCFD0548B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Munka1!$A$1:$D$15</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -122,7 +125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -194,45 +197,6 @@
       <top/>
       <bottom style="thin">
         <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -329,19 +293,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -642,15 +606,16 @@
   <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="1" max="1" width="8.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -674,7 +639,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -684,7 +649,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="9"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="14" t="s">
         <v>12</v>
       </c>
@@ -692,7 +657,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="9"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="14" t="s">
         <v>13</v>
       </c>
@@ -700,7 +665,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-      <c r="B8" s="10"/>
+      <c r="B8" s="11"/>
       <c r="C8" s="14" t="s">
         <v>14</v>
       </c>
@@ -758,7 +723,7 @@
     </row>
     <row r="14" spans="1:4" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="15" t="s">
@@ -769,6 +734,7 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="1">
